--- a/extenbooks/S609.xlsx
+++ b/extenbooks/S609.xlsx
@@ -904,7 +904,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>calculated</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S609.xlsx
+++ b/extenbooks/S609.xlsx
@@ -793,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -892,7 +892,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1952–2025</t>
+          <t>1952-1989</t>
         </is>
       </c>
     </row>
@@ -954,54 +954,55 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S609-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S609 — NSW / National Income Share</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 6 — The Net Social Wage</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>**Source Table**: Appendix Ch6 — `Table6_3_NetSocialWage.csv`, column `nsw_ni_share`</t>
+          <t># S609 — NSW / National Income Share</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Units**: share</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Period**: 1952–1989 (book; S607 extends through 2024 via Table6_3_Extended)</t>
+          <t>**Chapter**: 6 — The Net Social Wage</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1010,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>**Content Type**: time_series</t>
+          <t>**Source Table**: Appendix Ch6 — `Table6_3_NetSocialWage.csv`, column `nsw_ni_share`</t>
         </is>
       </c>
     </row>
@@ -1017,31 +1018,39 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Status**: calculated</t>
+          <t>**Units**: share</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Period**: 1952–1989 (book; S607 extends through 2024 via Table6_3_Extended)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NSW as a share of National Income — Tonak's preferred normalization for public communication and cross-country comparison.</t>
+          <t>## Definition</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1062,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>## Source</t>
+          <t>NSW as a share of National Income — Tonak's preferred normalization for public communication and cross-country comparison.</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1074,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>`data/source/book_tables/Table6_3_NetSocialWage.csv` (digitized from book Appendix 6 tables). Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
+          <t>## Source</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1086,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>`data/source/book_tables/Table6_3_NetSocialWage.csv` (digitized from book Appendix 6 tables). Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1098,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Loaded directly from `nsw_ni_share` column of Table 6.3. The book pre-computes this share; the new build preserves it rather than recomputing from S607 / NI, since National Income is not yet a first-class series in the registry.</t>
+          <t>## Construction</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1110,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
+          <t>Loaded directly from `nsw_ni_share` column of Table 6.3. The book pre-computes this share; the new build preserves it rather than recomputing from S607 / NI, since National Income is not yet a first-class series in the registry.</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1122,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1952=-0.0337; 1989=-0.0219</t>
+          <t>## Reference Values (Validation Benchmarks)</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1134,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tolerance class: `share_series`. Validator script: `code/V03_validators/V03_S609_nsw_ni_share.py`. Both endpoints PASS.</t>
+          <t>1952=-0.0337; 1989=-0.0219</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1146,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>## Provenance Chain</t>
+          <t>Tolerance class: `share_series`. Validator script: `code/V03_validators/V03_S609_nsw_ni_share.py`. Both endpoints PASS.</t>
         </is>
       </c>
     </row>
@@ -1149,23 +1158,19 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>## Provenance Chain</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>data/source/book_tables/Table6_3_NetSocialWage.csv</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S609_nsw_ni_share.py</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1178,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S609.csv</t>
+          <t>data/source/book_tables/Table6_3_NetSocialWage.csv</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1186,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S609_nsw_ni_share.py</t>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S609_nsw_ni_share.py</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1194,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S609.csv</t>
+          <t xml:space="preserve">       └── data/intermediate/S609.csv</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1202,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S609_nsw_ni_share.py</t>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S609_nsw_ni_share.py</t>
         </is>
       </c>
     </row>
@@ -1205,19 +1210,23 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">                 └── data/final/S609.csv</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S609_nsw_ni_share.py</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>## Citation</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1238,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 6 — The Net Social Wage. Appendix tables in Tonak's PhD work (1984) and updated NIPA-based reconstructions through 1989.</t>
+          <t>## Citation</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1250,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 6 — The Net Social Wage. Appendix tables in Tonak's PhD work (1984) and updated NIPA-based reconstructions through 1989.</t>
         </is>
       </c>
     </row>
@@ -1252,6 +1261,18 @@
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
         </is>
@@ -1268,12 +1289,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="54" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1296,154 +1317,244 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S609 = S607 / NI, where S607 is the Net Social Wage and NI is National Income from NIPA Table 1.7.5. This ratio expresses the net fiscal transfer as a share of total national income, providing a macroeconomic scale measure of the state's redistributive impact on workers.</t>
+          <t>Our adjustment procedure involves two steps. First, we estimate the social benefit expenditures directed toward wage and salary earners by the state, the taxes paid by them, and the difference between the two, which is the net transfer (a positive number when benefits exceed taxes and negative in the opposite case). The true compensation of wage and salary earners is their apparent compensation plus the net transfer. The tax, benefits, and net transfer rates are also calculated relative to the apparent employee compensation.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch6; CHAPTER_6_INVESTIGATION.md</t>
+          <t>ST_1994, Ch5 Section 5.9, p.137</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Numerator from S607 (NSW). Denominator is National Income from BEA NIPA Table 1.7.5 (National Income by Type of Income). Both in current dollars; ratio is dimensionless.</t>
+          <t>However, it should be noted that, where such calculations have been made, they greatly strengthen our conclusion that the net balance is strongly against the working population; that is, U.S. workers pay a net tax to the state, rather than receiving a net subsidy from it in the form of some 'social wage' (Miller 1989).</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BEA NIPA Table 1.7.5</t>
+          <t>ST_1994, Ch5 Section 5.9, p.141</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>empirical_finding</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NSW/NI is typically -1% to -4% during 1952-1989, indicating the state extracts 1-4% of national income net from workers. During the post-2001 positive-NSW era, the ratio rises to +1% to +3% in normal years. The COVID peak in 2020 reached +9.23% of NI, an unprecedented fiscal transfer to workers.</t>
+          <t>Appendix N lists the detailed calculations of our social accounting of taxes and benefits. Figure 5.22 shows the resulting tax and benefit rates (relative to total employee compensation), and Figure 5.23 shows the corresponding net transfer rate for the United States from 1952 to 1985.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CHAPTER_6_INVESTIGATION.md; NSW_COMPARISON_REVIEW.md</t>
+          <t>ST_1994, Ch5 Section 5.9, p.141</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cross_study_comparison</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Moos reconciled data (54 years, 1952-2012) provides NSW/NI benchmarks. AS2 and Moos track within 1 percentage point for most years. The divergence is largest in the 1970s-1980s where sales/excise tax treatment differences compound. All studies agree on the sign (negative) through the 1990s.</t>
+          <t>Net effect: 0-4% of EC extracted as net tax. Workers receive 29-30% of EC back as benefits by 1980s BUT workers pay 30-32% of EC in taxes.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>moos_nsw_reconciled.csv; NSW_COMPARISON_REVIEW.md</t>
+          <t>ST_1994, Appendix N significance; KB chunk_38 lines 452-455</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>theoretical_significance</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NSW/NI provides the most accessible measure of the state's net fiscal impact on workers. A persistently negative ratio challenges the conventional welfare-state narrative. The post-2001 sign reversal marks a genuine structural transformation in the fiscal relationship between the state and the working class, driven by entitlement expansion outpacing revenue growth.</t>
+          <t>Net transfer rate (Ntrrate) = (B1 - T1) / EC (S &amp; T, ratio).</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ST_1994, Ch6; Shaikh_Tonak_2002</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+          <t>ST_1994, Table N.2 variable definitions; KB chunk_38 line 337</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Validates Marxian state theory: State appears to provide social services - But taxes workers more than benefits received - Net effect: State facilitates transfer of surplus to capital - 'Faux frais of capitalist society' (Marx) - costs of system reproduction borne by workers.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N significance; KB chunk_38 lines 467-471</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ratio of Net Social Wage to National Income (S607/NI). Macroeconomic scale measure: typically -1% to -4% during 1952-1989, turning positive post-2001, peaking at +9.23% during COVID (2020).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>Net transfer is negative over most of 1952-85 period -&gt; net tax on workers. Reference: Shaikh and Tonak (1987) for detailed methodology.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N concept + reference; KB chunk_38 lines 210-212</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1971: +0.01 (+1%) -&gt; ONLY YEAR with positive net transfer.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.2 Ntrrate 1971; KB chunk_38 line 369</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>methodology_description</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S609 = S607 / NI, where S607 is the Net Social Wage and NI is National Income from NIPA Table 1.7.5. This ratio expresses the net fiscal transfer as a share of total national income, providing a macroeconomic scale measure of the state's redistributive impact on workers.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch6; CHAPTER_6_INVESTIGATION.md</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Inherits all known issues from S607 (NSW)</t>
+          <t>Numerator from S607 (NSW). Denominator is National Income from BEA NIPA Table 1.7.5 (National Income by Type of Income). Both in current dollars; ratio is dimensionless.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BEA NIPA Table 1.7.5</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>empirical_finding</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NI definition may shift with NIPA comprehensive revisions</t>
+          <t>NSW/NI is typically -1% to -4% during 1952-1989, indicating the state extracts 1-4% of national income net from workers. During the post-2001 positive-NSW era, the ratio rises to +1% to +3% in normal years. The COVID peak in 2020 reached +9.23% of NI, an unprecedented fiscal transfer to workers.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CHAPTER_6_INVESTIGATION.md; NSW_COMPARISON_REVIEW.md</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cross_study_comparison</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>COVID-era ratio (+9.23%) is an extreme outlier driven by emergency legislation</t>
+          <t>Moos reconciled data (54 years, 1952-2012) provides NSW/NI benchmarks. AS2 and Moos track within 1 percentage point for most years. The divergence is largest in the 1970s-1980s where sales/excise tax treatment differences compound. All studies agree on the sign (negative) through the 1990s.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>moos_nsw_reconciled.csv; NSW_COMPARISON_REVIEW.md</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>theoretical_significance</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Post-2001 positive ratio partly reflects demographic shift (aging population drawing more benefits)</t>
+          <t>NSW/NI provides the most accessible measure of the state's net fiscal impact on workers. A persistently negative ratio challenges the conventional welfare-state narrative. The post-2001 sign reversal marks a genuine structural transformation in the fiscal relationship between the state and the working class, driven by entitlement expansion outpacing revenue growth.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch6; Shaikh_Tonak_2002</t>
         </is>
       </c>
     </row>
     <row r="15"/>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>S607</t>
+          <t>Our adjustment procedure involves two steps. First, we estimate the social benefit expenditures directed toward wage and salary earners by the state, the taxes paid by them, and the difference between the two, which is the net transfer (a positive number when benefits exceed taxes and negative in the opposite case). The true compensation of wage and salary earners is their apparent compensation plus the net transfer. The tax, benefits, and net transfer rates are also calculated relative to the apparent employee compensation.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5 Section 5.9, p.137</t>
         </is>
       </c>
     </row>
@@ -1451,61 +1562,221 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
+          <t>However, it should be noted that, where such calculations have been made, they greatly strengthen our conclusion that the net balance is strongly against the working population; that is, U.S. workers pay a net tax to the state, rather than receiving a net subsidy from it in the form of some 'social wage' (Miller 1989).</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5 Section 5.9, p.141</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Appendix N lists the detailed calculations of our social accounting of taxes and benefits. Figure 5.22 shows the resulting tax and benefit rates (relative to total employee compensation), and Figure 5.23 shows the corresponding net transfer rate for the United States from 1952 to 1985.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5 Section 5.9, p.141</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Net effect: 0-4% of EC extracted as net tax. Workers receive 29-30% of EC back as benefits by 1980s BUT workers pay 30-32% of EC in taxes.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N significance; KB chunk_38 lines 452-455</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Net transfer rate (Ntrrate) = (B1 - T1) / EC (S &amp; T, ratio).</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.2 variable definitions; KB chunk_38 line 337</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Validates Marxian state theory: State appears to provide social services - But taxes workers more than benefits received - Net effect: State facilitates transfer of surplus to capital - 'Faux frais of capitalist society' (Marx) - costs of system reproduction borne by workers.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N significance; KB chunk_38 lines 467-471</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Net transfer is negative over most of 1952-85 period -&gt; net tax on workers. Reference: Shaikh and Tonak (1987) for detailed methodology.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N concept + reference; KB chunk_38 lines 210-212</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1971: +0.01 (+1%) -&gt; ONLY YEAR with positive net transfer.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.2 Ntrrate 1971; KB chunk_38 line 369</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ratio of Net Social Wage to National Income (S607/NI). Macroeconomic scale measure: typically -1% to -4% during 1952-1989, turning positive post-2001, peaking at +9.23% during COVID (2020).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Inherits all known issues from S607 (NSW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NI definition may shift with NIPA comprehensive revisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>COVID-era ratio (+9.23%) is an extreme outlier driven by emergency legislation</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Post-2001 positive ratio partly reflects demographic shift (aging population drawing more benefits)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>S607</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>S504</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>citations:</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>BEA_NIPA</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Bureau of Economic Analysis. National Income and Product Accounts. https://apps.bea.gov/iTable/</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Shaikh_Tonak_2002</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 2002. 'The Rise and Fall of the U.S. Welfare State.' In Political Economy and Contemporary Capitalism, ed. R. Baiman et al.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Moos_2017</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Moos, Julie. 2017. The Net Social Wage in the United States, 1952-2012. PhD dissertation.</t>
         </is>
@@ -1522,7 +1793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1593,7 +1864,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1885,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1952": -0.0337, "1989": -0.0219}</t>
         </is>
       </c>
     </row>
@@ -1639,6 +1910,42 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.02</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S609.xlsx
+++ b/extenbooks/S609.xlsx
@@ -1110,7 +1110,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Loaded directly from `nsw_ni_share` column of Table 6.3. The book pre-computes this share; the new build preserves it rather than recomputing from S607 / NI, since National Income is not yet a first-class series in the registry.</t>
+          <t>Loaded directly from the `nsw_ni_share` column of the project-internal reconstruction file `Table6_3_NetSocialWage.csv` (an internal label — the book has no Table 6.3; the underlying book source is Chapter 5 §5.9 / Appendix N). The share is pre-computed in that reconstruction; the build preserves it rather than recomputing from S607 / NI, since National Income is not yet a first-class series in the registry.</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S609.xlsx
+++ b/extenbooks/S609.xlsx
@@ -447,11 +447,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,7 +463,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>S&amp;T 1994, units=share</t>
+          <t>S607-A(book) / NI(NIPA), units=share</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Table6_3_NetSocialWage.csv:nsw_ni_share, units=share</t>
         </is>
       </c>
     </row>
@@ -475,6 +481,11 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>S609-A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>S609-RECON-A</t>
         </is>
       </c>
     </row>
@@ -483,6 +494,9 @@
         <v>1952</v>
       </c>
       <c r="B3" s="3" t="n">
+        <v>-0.048657</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>-0.0337</v>
       </c>
     </row>
@@ -491,6 +505,9 @@
         <v>1953</v>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-0.042179</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-0.0309</v>
       </c>
     </row>
@@ -499,6 +516,9 @@
         <v>1954</v>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-0.027657</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-0.0226</v>
       </c>
     </row>
@@ -507,6 +527,9 @@
         <v>1955</v>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-0.034794</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-0.0303</v>
       </c>
     </row>
@@ -515,6 +538,9 @@
         <v>1956</v>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-0.035145</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-0.0389</v>
       </c>
     </row>
@@ -523,6 +549,9 @@
         <v>1957</v>
       </c>
       <c r="B8" s="3" t="n">
+        <v>-0.028048</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>-0.0356</v>
       </c>
     </row>
@@ -531,6 +560,9 @@
         <v>1958</v>
       </c>
       <c r="B9" s="3" t="n">
+        <v>-0.013678</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>-0.0186</v>
       </c>
     </row>
@@ -539,6 +571,9 @@
         <v>1959</v>
       </c>
       <c r="B10" s="3" t="n">
+        <v>-0.020916</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>-0.0336</v>
       </c>
     </row>
@@ -547,6 +582,9 @@
         <v>1960</v>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-0.028107</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-0.0451</v>
       </c>
     </row>
@@ -555,6 +593,9 @@
         <v>1961</v>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-0.01386</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-0.0363</v>
       </c>
     </row>
@@ -563,6 +604,9 @@
         <v>1962</v>
       </c>
       <c r="B13" s="3" t="n">
+        <v>-0.020966</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>-0.0416</v>
       </c>
     </row>
@@ -571,6 +615,9 @@
         <v>1963</v>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-0.028076</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-0.0458</v>
       </c>
     </row>
@@ -579,6 +626,9 @@
         <v>1964</v>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-0.015351</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-0.039</v>
       </c>
     </row>
@@ -587,6 +637,9 @@
         <v>1965</v>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-0.01403</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>-0.0378</v>
       </c>
     </row>
@@ -595,6 +648,9 @@
         <v>1966</v>
       </c>
       <c r="B17" s="3" t="n">
+        <v>-0.021432</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>-0.0429</v>
       </c>
     </row>
@@ -603,6 +659,9 @@
         <v>1967</v>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-0.014284</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>-0.033</v>
       </c>
     </row>
@@ -611,6 +670,9 @@
         <v>1968</v>
       </c>
       <c r="B19" s="3" t="n">
+        <v>-0.021549</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>-0.0361</v>
       </c>
     </row>
@@ -619,6 +681,9 @@
         <v>1969</v>
       </c>
       <c r="B20" s="3" t="n">
+        <v>-0.03611</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>-0.0467</v>
       </c>
     </row>
@@ -627,6 +692,9 @@
         <v>1970</v>
       </c>
       <c r="B21" s="3" t="n">
+        <v>-0.014307</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>-0.0274</v>
       </c>
     </row>
@@ -635,6 +703,9 @@
         <v>1971</v>
       </c>
       <c r="B22" s="3" t="n">
+        <v>0.007056</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-0.0124</v>
       </c>
     </row>
@@ -643,6 +714,9 @@
         <v>1972</v>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-0.007098</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-0.0219</v>
       </c>
     </row>
@@ -651,6 +725,9 @@
         <v>1973</v>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-0.007114</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-0.0264</v>
       </c>
     </row>
@@ -659,6 +736,9 @@
         <v>1974</v>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-0.007116</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-0.0189</v>
       </c>
     </row>
@@ -667,6 +747,9 @@
         <v>1975</v>
       </c>
       <c r="B26" s="3" t="n">
+        <v>0.027804</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>0.0144</v>
       </c>
     </row>
@@ -675,6 +758,9 @@
         <v>1976</v>
       </c>
       <c r="B27" s="3" t="n">
+        <v>0.014167</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>0.0033</v>
       </c>
     </row>
@@ -683,6 +769,9 @@
         <v>1977</v>
       </c>
       <c r="B28" s="3" t="n">
+        <v>0.007039</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-0.0055</v>
       </c>
     </row>
@@ -691,6 +780,9 @@
         <v>1978</v>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-0.00715</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>-0.0146</v>
       </c>
     </row>
@@ -699,6 +791,9 @@
         <v>1979</v>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-0.014321</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-0.0191</v>
       </c>
     </row>
@@ -707,6 +802,9 @@
         <v>1980</v>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-0.00701</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-0.007900000000000001</v>
       </c>
     </row>
@@ -715,6 +813,9 @@
         <v>1981</v>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-0.006932</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>-0.0161</v>
       </c>
     </row>
@@ -723,6 +824,9 @@
         <v>1982</v>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-0.006721</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-0.0023</v>
       </c>
     </row>
@@ -731,6 +835,9 @@
         <v>1983</v>
       </c>
       <c r="B34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>0.003</v>
       </c>
     </row>
@@ -739,6 +846,9 @@
         <v>1984</v>
       </c>
       <c r="B35" s="3" t="n">
+        <v>-0.013539</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>-0.008699999999999999</v>
       </c>
     </row>
@@ -747,6 +857,9 @@
         <v>1985</v>
       </c>
       <c r="B36" s="3" t="n">
+        <v>-0.020093</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>-0.0121</v>
       </c>
     </row>
@@ -755,6 +868,9 @@
         <v>1986</v>
       </c>
       <c r="B37" s="3" t="n">
+        <v>-0.013498</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>-0.0111</v>
       </c>
     </row>
@@ -763,6 +879,9 @@
         <v>1987</v>
       </c>
       <c r="B38" s="3" t="n">
+        <v>-0.020427</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>-0.0194</v>
       </c>
     </row>
@@ -771,6 +890,9 @@
         <v>1988</v>
       </c>
       <c r="B39" s="3" t="n">
+        <v>-0.020334</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>-0.022</v>
       </c>
     </row>
@@ -779,6 +901,9 @@
         <v>1989</v>
       </c>
       <c r="B40" s="3" t="n">
+        <v>-0.026701</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>-0.0219</v>
       </c>
     </row>
@@ -793,7 +918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B62"/>
+  <dimension ref="A1:B72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -973,44 +1098,48 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S&amp;T 1994</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+          <t>S607-A(book) / NI(NIPA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S609-RECON-A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Table6_3_NetSocialWage.csv:nsw_ni_share</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t># S609 — NSW / National Income Share</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t># S609 — NSW / National Income Share</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>**Chapter**: 6 — The Net Social Wage</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>**Source Table**: Appendix Ch6 — `Table6_3_NetSocialWage.csv`, column `nsw_ni_share`</t>
+          <t>**Chapter**: 6 — The Net Social Wage</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1147,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Units**: share</t>
+          <t>**Source Table**: Appendix Ch6 — `Table6_3_NetSocialWage.csv`, column `nsw_ni_share`</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1155,7 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>**Period**: 1952–1989 (book; S607 extends through 2024 via Table6_3_Extended)</t>
+          <t>**Units**: share</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1163,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>**Content Type**: time_series</t>
+          <t>**Period**: 1952–1989 (book; S607 extends through 2024 via Table6_3_Extended)</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1171,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
@@ -1050,135 +1179,135 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>NSW as a share of National Income — Tonak's preferred normalization for public communication and cross-country comparison.</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NSW as a share of National Income — Tonak's preferred normalization for public communication and cross-country comparison.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>## Source</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>## Source</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>`data/source/book_tables/Table6_3_NetSocialWage.csv` (digitized from book Appendix 6 tables). Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>`data/source/book_tables/Table6_3_NetSocialWage.csv` (digitized from book Appendix 6 tables). Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>## Construction</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Loaded directly from the `nsw_ni_share` column of the project-internal reconstruction file `Table6_3_NetSocialWage.csv` (an internal label — the book has no Table 6.3; the underlying book source is Chapter 5 §5.9 / Appendix N). The share is pre-computed in that reconstruction; the build preserves it rather than recomputing from S607 / NI, since National Income is not yet a first-class series in the registry.</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Loaded directly from the `nsw_ni_share` column of the project-internal reconstruction file `Table6_3_NetSocialWage.csv` (an internal label — the book has no Table 6.3; the underlying book source is Chapter 5 §5.9 / Appendix N). The share is pre-computed in that reconstruction; the build preserves it rather than recomputing from S607 / NI, since National Income is not yet a first-class series in the registry.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>## Reference Values (Validation Benchmarks)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>1952=-0.0337; 1989=-0.0219</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1952=-0.0337; 1989=-0.0219</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Tolerance class: `share_series`. Validator script: `code/V03_validators/V03_S609_nsw_ni_share.py`. Both endpoints PASS.</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Tolerance class: `share_series`. Validator script: `code/V03_validators/V03_S609_nsw_ni_share.py`. Both endpoints PASS.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>## Provenance Chain</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>## Provenance Chain</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>data/source/book_tables/Table6_3_NetSocialWage.csv</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1315,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S609_nsw_ni_share.py</t>
+          <t>data/source/book_tables/Table6_3_NetSocialWage.csv</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1323,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S609.csv</t>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S609_nsw_ni_share.py</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1331,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S609_nsw_ni_share.py</t>
+          <t xml:space="preserve">       └── data/intermediate/S609.csv</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1339,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S609.csv</t>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S609_nsw_ni_share.py</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1347,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S609_nsw_ni_share.py</t>
+          <t xml:space="preserve">                 └── data/final/S609.csv</t>
         </is>
       </c>
     </row>
@@ -1226,55 +1355,115 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S609_nsw_ni_share.py</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>## Citation</t>
-        </is>
-      </c>
+      <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>## Citation</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 6 — The Net Social Wage. Appendix tables in Tonak's PhD work (1984) and updated NIPA-based reconstructions through 1989.</t>
-        </is>
-      </c>
+      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 6 — The Net Social Wage. Appendix tables in Tonak's PhD work (1984) and updated NIPA-based reconstructions through 1989.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr">
+      <c r="B62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>## D3 book-faithful adoption (2026-07-02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>**S609-A recomputed** as book-faithful NSW / NIPA NI. The book publishes NO NSW/NI table, so the numerator is book-faithful and the denominator NI is the NIPA reconstruction (documented hybrid; no independent book anchor). Reconstruction preserved as **S609-RECON-A**.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>&gt; Decision: ADOPT NSW Candidate A (Appendix N Tables N.1/N.2 verbatim, 1952-1989) as book-period primary; BEA-API reconstruction becomes the labeled comparison/extension arm. Nothing deleted (.pre_d3 backups + -RECON subseries). See Handoffs/REVIEW_2026-07/D3_REGISTRY_PATCHES.json + D3_DIV_PATCHES.json.</t>
         </is>
       </c>
     </row>
@@ -1885,7 +2074,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"1952": -0.0337, "1989": -0.0219}</t>
+          <t>{"1952": -0.048657, "1989": -0.026701}</t>
         </is>
       </c>
     </row>
